--- a/MEDICAMENTS.xlsx
+++ b/MEDICAMENTS.xlsx
@@ -1,34 +1,219 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\gestion pharmacie - Copie\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10450" windowHeight="7030"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medicaments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Medicaments" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+  <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>Nom du medicament</t>
+  </si>
+  <si>
+    <t>Dossage (ml/mg)</t>
+  </si>
+  <si>
+    <t>Categorie</t>
+  </si>
+  <si>
+    <t>Quantite en stock</t>
+  </si>
+  <si>
+    <t>Date expiration</t>
+  </si>
+  <si>
+    <t>Prix d'achat</t>
+  </si>
+  <si>
+    <t>Prix de vente</t>
+  </si>
+  <si>
+    <t>Fournisseur</t>
+  </si>
+  <si>
+    <t>Amoxicilline</t>
+  </si>
+  <si>
+    <t>500 mg</t>
+  </si>
+  <si>
+    <t>Antibiotique</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>01/01/2021</t>
+  </si>
+  <si>
+    <t>mohamed</t>
+  </si>
+  <si>
+    <t>10g</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>01/02/2021</t>
+  </si>
+  <si>
+    <t>adnane</t>
+  </si>
+  <si>
+    <t>Glucophage</t>
+  </si>
+  <si>
+    <t>850 mg</t>
+  </si>
+  <si>
+    <t>Antidiabétique</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>01/03/2021</t>
+  </si>
+  <si>
+    <t>hamid</t>
+  </si>
+  <si>
+    <t>Voltarène</t>
+  </si>
+  <si>
+    <t>75 mg</t>
+  </si>
+  <si>
+    <t>Anti-inflammatoire</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>01/04/2021</t>
+  </si>
+  <si>
+    <t>reda</t>
+  </si>
+  <si>
+    <t>Mopral</t>
+  </si>
+  <si>
+    <t>20 mg</t>
+  </si>
+  <si>
+    <t>Anti-ulcéreux</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>01/05/2021</t>
+  </si>
+  <si>
+    <t>Gaviscon</t>
+  </si>
+  <si>
+    <t>Sachet</t>
+  </si>
+  <si>
+    <t>Anti-acide</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>01/06/2021</t>
+  </si>
+  <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
+    <t>Amlor</t>
+  </si>
+  <si>
+    <t>5 mg</t>
+  </si>
+  <si>
+    <t>Antihypertenseur</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>01/07/2021</t>
+  </si>
+  <si>
+    <t>Doliprane</t>
+  </si>
+  <si>
+    <t>1000 mg</t>
+  </si>
+  <si>
+    <t>Analgésique / Antipyrétique</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>01/08/2021</t>
+  </si>
+  <si>
+    <t>Aprovel</t>
+  </si>
+  <si>
+    <t>150 mg</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>01/09/2021</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>01/10/2021</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +232,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,104 +534,336 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>N°</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nom du medicament</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Dossage (ml/mg)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Categorie</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Quantite en stock</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date expiration</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Prix d'achat</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Prix de vente</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Fournisseur</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>azer</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Analgésiques</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AZER</t>
-        </is>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2">
+        <v>150</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>180</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>120</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <v>150</v>
+      </c>
+      <c r="I6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>133</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9">
+        <v>180</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11">
+        <v>150</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
